--- a/output_boron/boron_Intermediate_brown_2022.xlsx
+++ b/output_boron/boron_Intermediate_brown_2022.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1038/s41561-022-00982-7</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_brown_2022.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_brown_2022_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Zeeden, C. et al., 2013. Revised Miocene splice, astronomical tuning and calcareous plankton biochronology of ODP Site 926 between 5 and 14.4Ma. Palaeogeogr. Palaeoclimatol. Palaeoecol. 369, 430–451.Wilkens, R. H. et al., 2017. Revisiting the Ceara Rise, equatorial Atlantic Ocean: isotope stratigraphy of ODP Leg 154 from 0 to 5Ma. Clim. Past 13, 779–793.</t>
+    <t xml:space="preserve">Zeeden, C. et al., 2013. Revised Miocene splice, astronomical tuning and calcareous plankton biochronology of ODP Site 926 between 5 and 14.4Ma. Palaeogeogr. Palaeoclimatol. Palaeoecol. 369, 430–451.Wilkens, R. H. et al., 2017. Revisiting the Ceara Rise, equatorial Atlantic Ocean: isotope stratigraphy of ODP Leg 154 from 0 to 5Ma. Clim. Past 13, 779–793.; added age uncertainties based nannofossil biostratigraphy uncertainty reported by Zeeden et al.(2013) age model</t>
   </si>
   <si>
     <t xml:space="preserve">Trilobatus trilobus, Cibicidoides wuellerstorfi</t>
@@ -1534,7 +1534,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1594,12 +1594,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1713,7 +1707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1795,7 +1789,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2402,7 +2395,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2420,8 +2413,8 @@
       <c r="H5" t="n">
         <v>4.93571538461539</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.015</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2479,7 +2472,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2497,8 +2490,8 @@
       <c r="H6" t="n">
         <v>4.97690909090909</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.015</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2556,7 +2549,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2574,8 +2567,8 @@
       <c r="H7" t="n">
         <v>4.99852892561983</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.015</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2633,7 +2626,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2651,8 +2644,8 @@
       <c r="H8" t="n">
         <v>5.05233584905661</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.015</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2710,7 +2703,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2728,8 +2721,8 @@
       <c r="H9" t="n">
         <v>5.0576774045099</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.015</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2787,7 +2780,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2805,8 +2798,8 @@
       <c r="H10" t="n">
         <v>5.11957894736842</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.015</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -2864,7 +2857,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2882,8 +2875,8 @@
       <c r="H11" t="n">
         <v>5.16889351851852</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.015</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -2941,7 +2934,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2959,8 +2952,8 @@
       <c r="H12" t="n">
         <v>5.17946913580247</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.015</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3018,7 +3011,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3036,8 +3029,8 @@
       <c r="H13" t="n">
         <v>5.19915277777778</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.015</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3095,7 +3088,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3113,8 +3106,8 @@
       <c r="H14" t="n">
         <v>5.23413333333333</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.015</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3172,7 +3165,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3190,8 +3183,8 @@
       <c r="H15" t="n">
         <v>5.2724</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.015</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3249,7 +3242,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3267,8 +3260,8 @@
       <c r="H16" t="n">
         <v>5.3055</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.015</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3326,7 +3319,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3344,8 +3337,8 @@
       <c r="H17" t="n">
         <v>5.35875609756098</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.015</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3403,7 +3396,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3421,8 +3414,8 @@
       <c r="H18" t="n">
         <v>5.38192682926829</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.015</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -3480,7 +3473,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3498,8 +3491,8 @@
       <c r="H19" t="n">
         <v>5.41683950617284</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.015</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -3557,7 +3550,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3575,8 +3568,8 @@
       <c r="H20" t="n">
         <v>5.45200980392157</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.015</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -3634,7 +3627,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3652,8 +3645,8 @@
       <c r="H21" t="n">
         <v>5.49402631578948</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.015</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -3711,7 +3704,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3729,8 +3722,8 @@
       <c r="H22" t="n">
         <v>5.53666666666667</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.015</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -3788,7 +3781,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3806,8 +3799,8 @@
       <c r="H23" t="n">
         <v>5.57955555555556</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.015</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -3865,7 +3858,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3883,8 +3876,8 @@
       <c r="H24" t="n">
         <v>5.6015641025641</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.015</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -3942,7 +3935,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -3960,8 +3953,8 @@
       <c r="H25" t="n">
         <v>5.65411111111111</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.015</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4019,7 +4012,7 @@
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4037,8 +4030,8 @@
       <c r="H26" t="n">
         <v>5.70816216216216</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.015</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4096,7 +4089,7 @@
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4114,8 +4107,8 @@
       <c r="H27" t="n">
         <v>5.71483783783784</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.015</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -4173,7 +4166,7 @@
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4191,8 +4184,8 @@
       <c r="H28" t="n">
         <v>5.76598809523809</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.015</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -4250,7 +4243,7 @@
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4268,8 +4261,8 @@
       <c r="H29" t="n">
         <v>5.80740425531915</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.015</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -4327,7 +4320,7 @@
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4345,8 +4338,8 @@
       <c r="H30" t="n">
         <v>5.85219480519481</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.015</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -4404,7 +4397,7 @@
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4422,8 +4415,8 @@
       <c r="H31" t="n">
         <v>5.8927037037037</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.015</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -4481,7 +4474,7 @@
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4499,8 +4492,8 @@
       <c r="H32" t="n">
         <v>5.971375</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.015</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -4558,7 +4551,7 @@
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4576,8 +4569,8 @@
       <c r="H33" t="n">
         <v>6.0185</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.015</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -4635,7 +4628,7 @@
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4653,8 +4646,8 @@
       <c r="H34" t="n">
         <v>6.06146153846154</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.015</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -4712,7 +4705,7 @@
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4730,8 +4723,8 @@
       <c r="H35" t="n">
         <v>6.1029375</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.015</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -4789,7 +4782,7 @@
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4807,8 +4800,8 @@
       <c r="H36" t="n">
         <v>6.22933333333333</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.015</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -4866,7 +4859,7 @@
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -4884,8 +4877,8 @@
       <c r="H37" t="n">
         <v>6.29175675675676</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.015</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -4943,7 +4936,7 @@
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -4961,8 +4954,8 @@
       <c r="H38" t="n">
         <v>6.29889189189189</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.015</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -5020,7 +5013,7 @@
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5038,8 +5031,8 @@
       <c r="H39" t="n">
         <v>6.34642857142857</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.015</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -5097,7 +5090,7 @@
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5115,8 +5108,8 @@
       <c r="H40" t="n">
         <v>6.38508333333333</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.015</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -5174,7 +5167,7 @@
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5192,8 +5185,8 @@
       <c r="H41" t="n">
         <v>6.45696551724138</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.015</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -5251,7 +5244,7 @@
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5269,8 +5262,8 @@
       <c r="H42" t="n">
         <v>6.50464705882353</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.015</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -5328,7 +5321,7 @@
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5346,8 +5339,8 @@
       <c r="H43" t="n">
         <v>6.56347674418605</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.015</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -5405,7 +5398,7 @@
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5423,8 +5416,8 @@
       <c r="H44" t="n">
         <v>6.58842528735632</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.015</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -5482,7 +5475,7 @@
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5500,8 +5493,8 @@
       <c r="H45" t="n">
         <v>6.6046</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.015</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -5559,7 +5552,7 @@
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5577,8 +5570,8 @@
       <c r="H46" t="n">
         <v>6.63252173913044</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.015</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -5636,7 +5629,7 @@
       <c r="B47" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" t="s">
         <v>242</v>
       </c>
       <c r="D47" t="s">
@@ -5654,8 +5647,8 @@
       <c r="H47" t="n">
         <v>6.77237024221453</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.015</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -5713,7 +5706,7 @@
       <c r="B48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" t="s">
         <v>242</v>
       </c>
       <c r="D48" t="s">
@@ -5731,8 +5724,8 @@
       <c r="H48" t="n">
         <v>6.78752505446622</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.015</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -5790,7 +5783,7 @@
       <c r="B49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" t="s">
         <v>242</v>
       </c>
       <c r="D49" t="s">
@@ -5808,8 +5801,8 @@
       <c r="H49" t="n">
         <v>6.93085714285714</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.015</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -6037,53 +6030,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
